--- a/data/analysis_gemini_3_6_flash/visual_event_eval_gemini_3_6_flash.xlsx
+++ b/data/analysis_gemini_3_6_flash/visual_event_eval_gemini_3_6_flash.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="50">
   <si>
     <t>event</t>
   </si>
@@ -689,22 +689,22 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>0.8</v>
+        <v>0.714</v>
       </c>
       <c r="C6">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>5</v>
@@ -1420,7 +1420,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1457,6 +1457,23 @@
         <v>42</v>
       </c>
     </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1668,10 +1685,10 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
       </c>
       <c r="E2" t="s">
         <v>47</v>
